--- a/template/XBRL_CoE_Checklist_Result.xlsx
+++ b/template/XBRL_CoE_Checklist_Result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/euna/Downloads/XBRL_Checklist_WebApp/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB132KN\Downloads\Vscode_wrk\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E68B92-E64E-D84D-A296-31D8793CEC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3019B2CA-9C63-47CF-A913-0B8C257422D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="24420" windowHeight="12880" xr2:uid="{81F61C7E-5D53-4B13-AF9E-85E105AAB38E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{81F61C7E-5D53-4B13-AF9E-85E105AAB38E}"/>
   </bookViews>
   <sheets>
     <sheet name="LEAD" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -666,9 +663,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1398,7 +1395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1444,22 +1441,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1531,7 +1528,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1561,7 +1558,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
@@ -1573,7 +1570,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
@@ -1585,7 +1582,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1597,31 +1594,31 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1633,7 +1630,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
@@ -1646,10 +1643,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1666,13 +1663,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1716,52 +1713,28 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1791,7 +1764,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1800,7 +1773,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1827,23 +1800,47 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{816015C2-C774-4D11-97C6-5EEF1696C771}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -12777,17 +12774,17 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="B2:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="70" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="70" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" style="70" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="8.83203125" style="70"/>
-    <col min="14" max="14" width="8.6640625" style="70" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="70"/>
+    <col min="1" max="1" width="3.69921875" style="70" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="70" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="8.796875" style="70"/>
+    <col min="14" max="14" width="8.69921875" style="70" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="70"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="30" customHeight="1">
+    <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -12805,7 +12802,7 @@
       <c r="N2" s="94"/>
       <c r="P2" s="95"/>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B3" s="96" t="s">
         <v>88</v>
       </c>
@@ -12822,16 +12819,16 @@
       <c r="M3" s="97"/>
       <c r="N3" s="98"/>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
       <c r="P4" s="99"/>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
       <c r="P5" s="99"/>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
       <c r="P6" s="99"/>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B11" s="44" t="str">
         <f>"Total"&amp;" :  "&amp;SUM(N14:N52)</f>
         <v>Total :  0</v>
@@ -12851,8 +12848,8 @@
       <c r="M11" s="100"/>
       <c r="N11" s="100"/>
     </row>
-    <row r="12" spans="2:16" ht="16" thickBot="1"/>
-    <row r="13" spans="2:16" ht="16" thickBot="1">
+    <row r="12" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="13" spans="2:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="27" t="s">
         <v>14</v>
       </c>
@@ -12866,20 +12863,20 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
       <c r="M13" s="20"/>
       <c r="N13" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:16">
-      <c r="B14" s="109">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B14" s="138">
         <v>1</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="104" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="51" t="s">
@@ -12900,9 +12897,9 @@
       </c>
       <c r="O14" s="79"/>
     </row>
-    <row r="15" spans="2:16">
-      <c r="B15" s="110"/>
-      <c r="C15" s="116"/>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B15" s="139"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="55" t="s">
         <v>69</v>
       </c>
@@ -12910,10 +12907,10 @@
       <c r="F15" s="56"/>
       <c r="G15" s="56"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="140"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="140"/>
-      <c r="L15" s="140"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
       <c r="M15" s="58"/>
       <c r="N15" s="37">
         <f>'Checklist_1-2'!B11</f>
@@ -12921,9 +12918,9 @@
       </c>
       <c r="O15" s="79"/>
     </row>
-    <row r="16" spans="2:16">
-      <c r="B16" s="110"/>
-      <c r="C16" s="116"/>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B16" s="139"/>
+      <c r="C16" s="105"/>
       <c r="D16" s="55" t="s">
         <v>18</v>
       </c>
@@ -12931,10 +12928,10 @@
       <c r="F16" s="56"/>
       <c r="G16" s="56"/>
       <c r="H16" s="56"/>
-      <c r="I16" s="142"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="142"/>
-      <c r="L16" s="142"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
       <c r="M16" s="58"/>
       <c r="N16" s="37">
         <f>'Checklist_1-3'!B11</f>
@@ -12942,9 +12939,9 @@
       </c>
       <c r="O16" s="79"/>
     </row>
-    <row r="17" spans="2:15" ht="16" thickBot="1">
-      <c r="B17" s="111"/>
-      <c r="C17" s="117"/>
+    <row r="17" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="140"/>
+      <c r="C17" s="106"/>
       <c r="D17" s="59" t="s">
         <v>19</v>
       </c>
@@ -12952,10 +12949,10 @@
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="143"/>
-      <c r="K17" s="143"/>
-      <c r="L17" s="143"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
       <c r="M17" s="22"/>
       <c r="N17" s="38">
         <f>'Checklist_1-4'!B11</f>
@@ -12963,11 +12960,11 @@
       </c>
       <c r="O17" s="79"/>
     </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="112">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B18" s="141">
         <v>2</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="104" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="80" t="s">
@@ -12977,10 +12974,10 @@
       <c r="F18" s="52"/>
       <c r="G18" s="52"/>
       <c r="H18" s="52"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="123"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="115"/>
       <c r="M18" s="54"/>
       <c r="N18" s="46">
         <f>'Checklist_2-1'!B11</f>
@@ -12988,9 +12985,9 @@
       </c>
       <c r="O18" s="79"/>
     </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="112"/>
-      <c r="C19" s="116"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B19" s="141"/>
+      <c r="C19" s="105"/>
       <c r="D19" s="81" t="s">
         <v>66</v>
       </c>
@@ -13009,9 +13006,9 @@
       </c>
       <c r="O19" s="79"/>
     </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="112"/>
-      <c r="C20" s="116"/>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B20" s="141"/>
+      <c r="C20" s="105"/>
       <c r="D20" s="17" t="s">
         <v>54</v>
       </c>
@@ -13030,9 +13027,9 @@
       </c>
       <c r="O20" s="79"/>
     </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="112"/>
-      <c r="C21" s="116"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B21" s="141"/>
+      <c r="C21" s="105"/>
       <c r="D21" s="16" t="s">
         <v>55</v>
       </c>
@@ -13051,9 +13048,9 @@
       </c>
       <c r="O21" s="79"/>
     </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="112"/>
-      <c r="C22" s="116"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B22" s="141"/>
+      <c r="C22" s="105"/>
       <c r="D22" s="17" t="s">
         <v>84</v>
       </c>
@@ -13061,10 +13058,10 @@
       <c r="F22" s="56"/>
       <c r="G22" s="56"/>
       <c r="H22" s="56"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="140"/>
-      <c r="L22" s="140"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
       <c r="M22" s="58"/>
       <c r="N22" s="49">
         <f>'Checklist_2-5'!$B$11</f>
@@ -13072,9 +13069,9 @@
       </c>
       <c r="O22" s="79"/>
     </row>
-    <row r="23" spans="2:15" ht="17.5" customHeight="1" thickBot="1">
-      <c r="B23" s="112"/>
-      <c r="C23" s="116"/>
+    <row r="23" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="141"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="87" t="s">
         <v>51</v>
       </c>
@@ -13082,22 +13079,22 @@
       <c r="F23" s="88"/>
       <c r="G23" s="88"/>
       <c r="H23" s="88"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="116"/>
       <c r="M23" s="26"/>
-      <c r="N23" s="37">
+      <c r="N23" s="47">
         <f>'Checklist_2-6'!$B$11</f>
         <v>0</v>
       </c>
       <c r="O23" s="79"/>
     </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="113">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B24" s="142">
         <v>3</v>
       </c>
-      <c r="C24" s="115" t="s">
+      <c r="C24" s="104" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="63" t="s">
@@ -13107,10 +13104,10 @@
       <c r="F24" s="52"/>
       <c r="G24" s="52"/>
       <c r="H24" s="52"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="126"/>
-      <c r="L24" s="127"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="119"/>
       <c r="M24" s="64"/>
       <c r="N24" s="39">
         <f>'Checklist_3-1'!B11</f>
@@ -13118,9 +13115,9 @@
       </c>
       <c r="O24" s="79"/>
     </row>
-    <row r="25" spans="2:15" ht="16" thickBot="1">
-      <c r="B25" s="112"/>
-      <c r="C25" s="116"/>
+    <row r="25" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="141"/>
+      <c r="C25" s="105"/>
       <c r="D25" s="65" t="s">
         <v>20</v>
       </c>
@@ -13128,10 +13125,10 @@
       <c r="F25" s="56"/>
       <c r="G25" s="56"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="135"/>
-      <c r="L25" s="136"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="128"/>
       <c r="M25" s="22"/>
       <c r="N25" s="47">
         <f>'Checklist_3-2'!B11</f>
@@ -13139,11 +13136,11 @@
       </c>
       <c r="O25" s="79"/>
     </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="113">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B26" s="142">
         <v>4</v>
       </c>
-      <c r="C26" s="115" t="s">
+      <c r="C26" s="104" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="63" t="s">
@@ -13153,10 +13150,10 @@
       <c r="F26" s="52"/>
       <c r="G26" s="52"/>
       <c r="H26" s="66"/>
-      <c r="I26" s="128"/>
-      <c r="J26" s="129"/>
-      <c r="K26" s="129"/>
-      <c r="L26" s="130"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="122"/>
       <c r="M26" s="64"/>
       <c r="N26" s="36">
         <f>'Checklist_4-1'!B11</f>
@@ -13164,9 +13161,9 @@
       </c>
       <c r="O26" s="79"/>
     </row>
-    <row r="27" spans="2:15">
-      <c r="B27" s="112"/>
-      <c r="C27" s="116"/>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B27" s="141"/>
+      <c r="C27" s="105"/>
       <c r="D27" s="65" t="s">
         <v>23</v>
       </c>
@@ -13174,10 +13171,10 @@
       <c r="F27" s="56"/>
       <c r="G27" s="56"/>
       <c r="H27" s="56"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="133"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="124"/>
+      <c r="L27" s="125"/>
       <c r="M27" s="58"/>
       <c r="N27" s="42">
         <f>'Checklist_4-2'!B11</f>
@@ -13185,9 +13182,9 @@
       </c>
       <c r="O27" s="79"/>
     </row>
-    <row r="28" spans="2:15">
-      <c r="B28" s="112"/>
-      <c r="C28" s="116"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B28" s="141"/>
+      <c r="C28" s="105"/>
       <c r="D28" s="65" t="s">
         <v>24</v>
       </c>
@@ -13195,10 +13192,10 @@
       <c r="F28" s="56"/>
       <c r="G28" s="56"/>
       <c r="H28" s="56"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="133"/>
+      <c r="I28" s="123"/>
+      <c r="J28" s="124"/>
+      <c r="K28" s="124"/>
+      <c r="L28" s="125"/>
       <c r="M28" s="58"/>
       <c r="N28" s="42">
         <f>'Checklist_4-3'!B11</f>
@@ -13206,9 +13203,9 @@
       </c>
       <c r="O28" s="79"/>
     </row>
-    <row r="29" spans="2:15">
-      <c r="B29" s="112"/>
-      <c r="C29" s="116"/>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B29" s="141"/>
+      <c r="C29" s="105"/>
       <c r="D29" s="65" t="s">
         <v>25</v>
       </c>
@@ -13216,10 +13213,10 @@
       <c r="F29" s="56"/>
       <c r="G29" s="56"/>
       <c r="H29" s="56"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="133"/>
+      <c r="I29" s="123"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="124"/>
+      <c r="L29" s="125"/>
       <c r="M29" s="58"/>
       <c r="N29" s="42">
         <f>'Checklist_4-4'!B11</f>
@@ -13227,9 +13224,9 @@
       </c>
       <c r="O29" s="79"/>
     </row>
-    <row r="30" spans="2:15">
-      <c r="B30" s="112"/>
-      <c r="C30" s="116"/>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B30" s="141"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="65" t="s">
         <v>26</v>
       </c>
@@ -13237,10 +13234,10 @@
       <c r="F30" s="56"/>
       <c r="G30" s="56"/>
       <c r="H30" s="56"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="132"/>
-      <c r="K30" s="132"/>
-      <c r="L30" s="133"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="124"/>
+      <c r="L30" s="125"/>
       <c r="M30" s="58"/>
       <c r="N30" s="42">
         <f>'Checklist_4-5'!B11</f>
@@ -13248,9 +13245,9 @@
       </c>
       <c r="O30" s="79"/>
     </row>
-    <row r="31" spans="2:15" ht="16" thickBot="1">
-      <c r="B31" s="114"/>
-      <c r="C31" s="117"/>
+    <row r="31" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="143"/>
+      <c r="C31" s="106"/>
       <c r="D31" s="12" t="s">
         <v>27</v>
       </c>
@@ -13269,11 +13266,11 @@
       </c>
       <c r="O31" s="79"/>
     </row>
-    <row r="32" spans="2:15">
-      <c r="B32" s="103">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B32" s="135">
         <v>5</v>
       </c>
-      <c r="C32" s="106" t="s">
+      <c r="C32" s="132" t="s">
         <v>41</v>
       </c>
       <c r="D32" s="69" t="s">
@@ -13290,9 +13287,9 @@
       </c>
       <c r="O32" s="79"/>
     </row>
-    <row r="33" spans="2:15">
-      <c r="B33" s="104"/>
-      <c r="C33" s="107"/>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B33" s="136"/>
+      <c r="C33" s="133"/>
       <c r="D33" s="16" t="s">
         <v>47</v>
       </c>
@@ -13300,10 +13297,10 @@
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="138"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="139"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="131"/>
       <c r="M33" s="58"/>
       <c r="N33" s="37">
         <f>'Checklist_5-2'!B11</f>
@@ -13311,9 +13308,9 @@
       </c>
       <c r="O33" s="79"/>
     </row>
-    <row r="34" spans="2:15">
-      <c r="B34" s="104"/>
-      <c r="C34" s="107"/>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B34" s="136"/>
+      <c r="C34" s="133"/>
       <c r="D34" s="16" t="s">
         <v>50</v>
       </c>
@@ -13332,9 +13329,9 @@
       </c>
       <c r="O34" s="79"/>
     </row>
-    <row r="35" spans="2:15">
-      <c r="B35" s="104"/>
-      <c r="C35" s="107"/>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B35" s="136"/>
+      <c r="C35" s="133"/>
       <c r="D35" s="16" t="s">
         <v>49</v>
       </c>
@@ -13353,9 +13350,9 @@
       </c>
       <c r="O35" s="79"/>
     </row>
-    <row r="36" spans="2:15">
-      <c r="B36" s="104"/>
-      <c r="C36" s="107"/>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B36" s="136"/>
+      <c r="C36" s="133"/>
       <c r="D36" s="16" t="s">
         <v>80</v>
       </c>
@@ -13374,9 +13371,9 @@
       </c>
       <c r="O36" s="79"/>
     </row>
-    <row r="37" spans="2:15" ht="16" thickBot="1">
-      <c r="B37" s="105"/>
-      <c r="C37" s="108"/>
+    <row r="37" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="137"/>
+      <c r="C37" s="134"/>
       <c r="D37" s="16" t="s">
         <v>87</v>
       </c>
@@ -13395,11 +13392,11 @@
       </c>
       <c r="O37" s="102"/>
     </row>
-    <row r="38" spans="2:15">
-      <c r="B38" s="103">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B38" s="135">
         <v>6</v>
       </c>
-      <c r="C38" s="106" t="s">
+      <c r="C38" s="132" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="75" t="s">
@@ -13420,9 +13417,9 @@
       </c>
       <c r="O38" s="79"/>
     </row>
-    <row r="39" spans="2:15">
-      <c r="B39" s="104"/>
-      <c r="C39" s="107"/>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B39" s="136"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="17" t="s">
         <v>85</v>
       </c>
@@ -13441,9 +13438,9 @@
       </c>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="2:15" ht="16" thickBot="1">
-      <c r="B40" s="105"/>
-      <c r="C40" s="108"/>
+    <row r="40" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B40" s="137"/>
+      <c r="C40" s="134"/>
       <c r="D40" s="12" t="s">
         <v>86</v>
       </c>
@@ -13451,10 +13448,10 @@
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
-      <c r="I40" s="134"/>
-      <c r="J40" s="135"/>
-      <c r="K40" s="135"/>
-      <c r="L40" s="136"/>
+      <c r="I40" s="126"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="128"/>
       <c r="M40" s="22"/>
       <c r="N40" s="47">
         <f>'Checklist_6-3'!B11</f>
@@ -13462,7 +13459,7 @@
       </c>
       <c r="O40" s="79"/>
     </row>
-    <row r="41" spans="2:15">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B41" s="34"/>
       <c r="C41" s="13"/>
       <c r="D41" s="69" t="s">
@@ -13479,7 +13476,7 @@
       </c>
       <c r="O41" s="79"/>
     </row>
-    <row r="42" spans="2:15">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B42" s="23"/>
       <c r="C42" s="14"/>
       <c r="D42" s="17"/>
@@ -13495,7 +13492,7 @@
       <c r="N42" s="50"/>
       <c r="O42" s="79"/>
     </row>
-    <row r="43" spans="2:15">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B43" s="23"/>
       <c r="C43" s="14"/>
       <c r="D43" s="17"/>
@@ -13510,7 +13507,7 @@
       <c r="M43" s="25"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="2:15">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B44" s="23"/>
       <c r="C44" s="14"/>
       <c r="D44" s="16"/>
@@ -13525,7 +13522,7 @@
       <c r="M44" s="25"/>
       <c r="N44" s="24"/>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B45" s="34"/>
       <c r="C45" s="13"/>
       <c r="D45" s="16"/>
@@ -13540,7 +13537,7 @@
       <c r="M45" s="25"/>
       <c r="N45" s="24"/>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B46" s="34">
         <v>7</v>
       </c>
@@ -13559,7 +13556,7 @@
       <c r="M46" s="25"/>
       <c r="N46" s="24"/>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B47" s="23"/>
       <c r="C47" s="14"/>
       <c r="D47" s="16"/>
@@ -13574,7 +13571,7 @@
       <c r="M47" s="25"/>
       <c r="N47" s="24"/>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B48" s="23"/>
       <c r="C48" s="14"/>
       <c r="D48" s="16"/>
@@ -13589,7 +13586,7 @@
       <c r="M48" s="25"/>
       <c r="N48" s="24"/>
     </row>
-    <row r="49" spans="2:14">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B49" s="23"/>
       <c r="C49" s="14"/>
       <c r="D49" s="16"/>
@@ -13604,7 +13601,7 @@
       <c r="M49" s="25"/>
       <c r="N49" s="24"/>
     </row>
-    <row r="50" spans="2:14">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B50" s="23"/>
       <c r="C50" s="14"/>
       <c r="D50" s="16"/>
@@ -13619,7 +13616,7 @@
       <c r="M50" s="25"/>
       <c r="N50" s="24"/>
     </row>
-    <row r="51" spans="2:14">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B51" s="23"/>
       <c r="C51" s="14"/>
       <c r="D51" s="16"/>
@@ -13634,7 +13631,7 @@
       <c r="M51" s="25"/>
       <c r="N51" s="24"/>
     </row>
-    <row r="52" spans="2:14" ht="16" thickBot="1">
+    <row r="52" spans="2:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B52" s="26"/>
       <c r="C52" s="15"/>
       <c r="D52" s="12"/>
@@ -13642,20 +13639,23 @@
       <c r="F52" s="21"/>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
-      <c r="I52" s="118"/>
-      <c r="J52" s="119"/>
-      <c r="K52" s="119"/>
-      <c r="L52" s="120"/>
+      <c r="I52" s="110"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="112"/>
       <c r="M52" s="22"/>
       <c r="N52" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="B32:B37"/>
     <mergeCell ref="I52:L52"/>
     <mergeCell ref="C18:C23"/>
     <mergeCell ref="I18:L18"/>
@@ -13672,14 +13672,11 @@
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="C32:C37"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -13696,7 +13693,7 @@
     <hyperlink ref="N31" location="'Checklist_4-6'!A1" display="'Checklist_4-6'!A1" xr:uid="{5E204C6F-37A2-4E71-AC2D-EB1B0C9B63DA}"/>
     <hyperlink ref="N20" location="'Checklist_2-3'!A1" display="'Checklist_2-3'!A1" xr:uid="{6A3BF781-7501-426E-96A4-98688C6D6205}"/>
     <hyperlink ref="N21" location="'Checklist_2-4'!A1" display="'Checklist_2-4'!A1" xr:uid="{432C8327-7285-4987-9C7F-DDB33523808E}"/>
-    <hyperlink ref="N23" location="'Checklist_2-5'!A1" display="'Checklist_2-5'!A1" xr:uid="{540A151A-0C03-49D9-A744-5A794C5B89A0}"/>
+    <hyperlink ref="N23" location="'Checklist_2-6'!A1" display="'Checklist_2-6'!A1" xr:uid="{540A151A-0C03-49D9-A744-5A794C5B89A0}"/>
     <hyperlink ref="N32" location="'Checklist_5-1'!A1" display="'Checklist_5-1'!A1" xr:uid="{5420E0E8-D28F-4805-937A-AB2103CF9735}"/>
     <hyperlink ref="N33" location="'Checklist_5-2'!A1" display="'Checklist_5-2'!A1" xr:uid="{8BD4279B-9B3E-49AE-A970-56F11229ABCE}"/>
     <hyperlink ref="N35" location="'Checklist_5-4'!A1" display="'Checklist_5-4'!A1" xr:uid="{4859F800-0725-4D99-A190-D86A4CC6883B}"/>
@@ -13721,18 +13718,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC984A1-B8A4-4F7C-B160-641D73B7703E}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>83</v>
       </c>
@@ -13745,7 +13742,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -13758,7 +13755,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -13774,14 +13771,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -13836,18 +13833,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D319E4-EB67-4C2F-BB5E-C11C33C7B491}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>56</v>
       </c>
@@ -13860,7 +13857,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -13873,7 +13870,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -13889,14 +13886,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -13951,18 +13948,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AAFC1C-C5F3-43EF-A9E4-98A6C57B9F24}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="B2:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="30" customHeight="1">
+    <row r="2" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
@@ -13975,7 +13972,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -13988,7 +13985,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14004,14 +14001,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14051,18 +14048,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D9E888-8FB2-42A9-9CAD-8CC1F6168131}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="B2:L55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="30" customHeight="1">
+    <row r="2" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
@@ -14075,7 +14072,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14088,12 +14085,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14109,14 +14106,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14147,172 +14144,172 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
     </row>
-    <row r="17" spans="11:12">
+    <row r="17" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
     </row>
-    <row r="18" spans="11:12">
+    <row r="18" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="11:12">
+    <row r="19" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
     </row>
-    <row r="20" spans="11:12">
+    <row r="20" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="11:12">
+    <row r="21" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
     </row>
-    <row r="22" spans="11:12">
+    <row r="22" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="11:12">
+    <row r="23" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
-    <row r="24" spans="11:12">
+    <row r="24" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
     </row>
-    <row r="25" spans="11:12">
+    <row r="25" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
     </row>
-    <row r="26" spans="11:12">
+    <row r="26" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="11:12">
+    <row r="27" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="11:12">
+    <row r="28" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="11:12">
+    <row r="29" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="11:12">
+    <row r="30" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="11:12">
+    <row r="31" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
     </row>
-    <row r="32" spans="11:12">
+    <row r="32" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
     </row>
-    <row r="33" spans="11:12">
+    <row r="33" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
     </row>
-    <row r="34" spans="11:12">
+    <row r="34" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
     </row>
-    <row r="35" spans="11:12">
+    <row r="35" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
     </row>
-    <row r="36" spans="11:12">
+    <row r="36" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
     </row>
-    <row r="37" spans="11:12">
+    <row r="37" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
     </row>
-    <row r="38" spans="11:12">
+    <row r="38" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
     </row>
-    <row r="39" spans="11:12">
+    <row r="39" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
     </row>
-    <row r="40" spans="11:12">
+    <row r="40" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
     </row>
-    <row r="41" spans="11:12">
+    <row r="41" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
     </row>
-    <row r="42" spans="11:12">
+    <row r="42" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
     </row>
-    <row r="43" spans="11:12">
+    <row r="43" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
     </row>
-    <row r="44" spans="11:12">
+    <row r="44" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
     </row>
-    <row r="45" spans="11:12">
+    <row r="45" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
     </row>
-    <row r="46" spans="11:12">
+    <row r="46" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
     </row>
-    <row r="47" spans="11:12">
+    <row r="47" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
     </row>
-    <row r="48" spans="11:12">
+    <row r="48" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
     </row>
-    <row r="49" spans="11:12">
+    <row r="49" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
     </row>
-    <row r="50" spans="11:12">
+    <row r="50" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
     </row>
-    <row r="51" spans="11:12">
+    <row r="51" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
     </row>
-    <row r="52" spans="11:12">
+    <row r="52" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
     </row>
-    <row r="53" spans="11:12">
+    <row r="53" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
     </row>
-    <row r="54" spans="11:12">
+    <row r="54" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
     </row>
-    <row r="55" spans="11:12">
+    <row r="55" spans="11:12" x14ac:dyDescent="0.4">
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
     </row>
@@ -14327,18 +14324,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97D5772F-B5BA-4F05-A3F3-454C07BE2D42}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>42</v>
       </c>
@@ -14351,7 +14348,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14364,12 +14361,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14385,10 +14382,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14443,18 +14440,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D98A6E-C997-4CE5-9A0B-D798392B10C8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>43</v>
       </c>
@@ -14467,7 +14464,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14480,7 +14477,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14496,10 +14493,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14554,18 +14551,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78767311-9051-4C79-BC6B-2D0F74810CD4}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>44</v>
       </c>
@@ -14578,7 +14575,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14591,12 +14588,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14612,10 +14609,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14670,18 +14667,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F13E10-CC2D-47E7-BC08-F6D78F50246A}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>45</v>
       </c>
@@ -14694,7 +14691,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14707,7 +14704,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14723,10 +14720,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14781,18 +14778,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCF34A2-D0D4-444D-875B-DFFB08751F23}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>62</v>
       </c>
@@ -14805,7 +14802,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14821,7 +14818,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14837,10 +14834,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -14895,18 +14892,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E333C2A5-36FB-46A7-A988-B067F7E25A86}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
@@ -14919,7 +14916,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -14932,7 +14929,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -14948,10 +14945,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15006,18 +15003,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E43F18B-BC17-448F-ADFA-DD5922D17F36}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:W13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="30" customHeight="1">
+    <row r="2" spans="2:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>32</v>
       </c>
@@ -15030,7 +15027,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:23">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15043,12 +15040,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:23">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="2:23">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15064,14 +15061,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:23">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:23">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15124,18 +15121,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF309986-3512-4C4E-9E8B-47F3D8B9F148}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>57</v>
       </c>
@@ -15148,7 +15145,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15161,12 +15158,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15182,10 +15179,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15240,18 +15237,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F227487-05F7-4319-90B7-80833A452F4C}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>58</v>
       </c>
@@ -15264,7 +15261,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15277,12 +15274,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15298,10 +15295,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15356,18 +15353,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2754BE2-2CA5-48E5-8C0C-01134F227BAE}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>61</v>
       </c>
@@ -15380,7 +15377,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15393,12 +15390,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15414,10 +15411,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15472,18 +15469,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{255B70E4-46DF-43B3-8192-54EF753C8F6C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
@@ -15496,7 +15493,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15509,12 +15506,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15530,10 +15527,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15588,18 +15585,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAEBD7C5-2E98-4884-A014-DCBD73DB8384}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>81</v>
       </c>
@@ -15612,7 +15609,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15626,7 +15623,7 @@
       <c r="J3" s="5"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15642,10 +15639,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15699,18 +15696,18 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C2756E3-9127-40D5-8F5D-0B1E430FFAE1}">
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>89</v>
       </c>
@@ -15723,7 +15720,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15737,7 +15734,7 @@
       <c r="J3" s="5"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15753,10 +15750,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15799,18 +15796,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6141FFAD-28AC-418B-84F9-73847269EA70}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>37</v>
       </c>
@@ -15823,7 +15820,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15836,7 +15833,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15852,10 +15849,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -15910,18 +15907,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797EFB9B-0FB3-477C-8FE1-26A328674FF6}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>64</v>
       </c>
@@ -15934,7 +15931,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -15947,7 +15944,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -15963,10 +15960,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -16021,18 +16018,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F884745A-FF22-4B77-8B06-A2B8BCA882D8}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="B2:Y409"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>82</v>
       </c>
@@ -16045,7 +16042,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -16059,7 +16056,7 @@
       <c r="J3" s="5"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -16075,10 +16072,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -16122,7 +16119,7 @@
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B14" s="86"/>
       <c r="C14" s="86"/>
       <c r="D14" s="86"/>
@@ -16133,7 +16130,7 @@
       <c r="I14" s="86"/>
       <c r="J14" s="86"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B15" s="86"/>
       <c r="C15" s="86"/>
       <c r="D15" s="86"/>
@@ -16144,7 +16141,7 @@
       <c r="I15" s="86"/>
       <c r="J15" s="86"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B16" s="86"/>
       <c r="C16" s="86"/>
       <c r="D16" s="86"/>
@@ -16155,7 +16152,7 @@
       <c r="I16" s="86"/>
       <c r="J16" s="86"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B17" s="86"/>
       <c r="C17" s="86"/>
       <c r="D17" s="86"/>
@@ -16166,7 +16163,7 @@
       <c r="I17" s="86"/>
       <c r="J17" s="86"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B18" s="86"/>
       <c r="C18" s="86"/>
       <c r="D18" s="86"/>
@@ -16177,7 +16174,7 @@
       <c r="I18" s="86"/>
       <c r="J18" s="86"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="86"/>
       <c r="C19" s="86"/>
       <c r="D19" s="86"/>
@@ -16188,7 +16185,7 @@
       <c r="I19" s="86"/>
       <c r="J19" s="86"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B20" s="86"/>
       <c r="C20" s="86"/>
       <c r="D20" s="86"/>
@@ -16199,7 +16196,7 @@
       <c r="I20" s="86"/>
       <c r="J20" s="86"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B21" s="86"/>
       <c r="C21" s="86"/>
       <c r="D21" s="86"/>
@@ -16210,7 +16207,7 @@
       <c r="I21" s="86"/>
       <c r="J21" s="86"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B22" s="86"/>
       <c r="C22" s="86"/>
       <c r="D22" s="86"/>
@@ -16221,7 +16218,7 @@
       <c r="I22" s="86"/>
       <c r="J22" s="86"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B23" s="86"/>
       <c r="C23" s="86"/>
       <c r="D23" s="86"/>
@@ -16232,7 +16229,7 @@
       <c r="I23" s="86"/>
       <c r="J23" s="86"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B24" s="86"/>
       <c r="C24" s="86"/>
       <c r="D24" s="86"/>
@@ -16243,7 +16240,7 @@
       <c r="I24" s="86"/>
       <c r="J24" s="86"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B25" s="86"/>
       <c r="C25" s="86"/>
       <c r="D25" s="86"/>
@@ -16254,7 +16251,7 @@
       <c r="I25" s="86"/>
       <c r="J25" s="86"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B26" s="86"/>
       <c r="C26" s="86"/>
       <c r="D26" s="86"/>
@@ -16265,7 +16262,7 @@
       <c r="I26" s="86"/>
       <c r="J26" s="86"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B27" s="86"/>
       <c r="C27" s="86"/>
       <c r="D27" s="86"/>
@@ -16276,7 +16273,7 @@
       <c r="I27" s="86"/>
       <c r="J27" s="86"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B28" s="86"/>
       <c r="C28" s="86"/>
       <c r="D28" s="86"/>
@@ -16287,7 +16284,7 @@
       <c r="I28" s="86"/>
       <c r="J28" s="86"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B29" s="86"/>
       <c r="C29" s="86"/>
       <c r="D29" s="86"/>
@@ -16298,7 +16295,7 @@
       <c r="I29" s="86"/>
       <c r="J29" s="86"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B30" s="86"/>
       <c r="C30" s="86"/>
       <c r="D30" s="86"/>
@@ -16309,7 +16306,7 @@
       <c r="I30" s="86"/>
       <c r="J30" s="86"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B31" s="86"/>
       <c r="C31" s="86"/>
       <c r="D31" s="86"/>
@@ -16320,7 +16317,7 @@
       <c r="I31" s="86"/>
       <c r="J31" s="86"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B32" s="86"/>
       <c r="C32" s="86"/>
       <c r="D32" s="86"/>
@@ -16331,7 +16328,7 @@
       <c r="I32" s="86"/>
       <c r="J32" s="86"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B33" s="86"/>
       <c r="C33" s="86"/>
       <c r="D33" s="86"/>
@@ -16342,7 +16339,7 @@
       <c r="I33" s="86"/>
       <c r="J33" s="86"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B34" s="86"/>
       <c r="C34" s="86"/>
       <c r="D34" s="86"/>
@@ -16353,7 +16350,7 @@
       <c r="I34" s="86"/>
       <c r="J34" s="86"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B35" s="86"/>
       <c r="C35" s="86"/>
       <c r="D35" s="86"/>
@@ -16364,7 +16361,7 @@
       <c r="I35" s="86"/>
       <c r="J35" s="86"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B36" s="86"/>
       <c r="C36" s="86"/>
       <c r="D36" s="86"/>
@@ -16375,7 +16372,7 @@
       <c r="I36" s="86"/>
       <c r="J36" s="86"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B37" s="86"/>
       <c r="C37" s="86"/>
       <c r="D37" s="86"/>
@@ -16386,7 +16383,7 @@
       <c r="I37" s="86"/>
       <c r="J37" s="86"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B38" s="86"/>
       <c r="C38" s="86"/>
       <c r="D38" s="86"/>
@@ -16397,7 +16394,7 @@
       <c r="I38" s="86"/>
       <c r="J38" s="86"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B39" s="86"/>
       <c r="C39" s="86"/>
       <c r="D39" s="86"/>
@@ -16408,7 +16405,7 @@
       <c r="I39" s="86"/>
       <c r="J39" s="86"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B40" s="86"/>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -16419,7 +16416,7 @@
       <c r="I40" s="86"/>
       <c r="J40" s="86"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B41" s="86"/>
       <c r="C41" s="86"/>
       <c r="D41" s="86"/>
@@ -16430,7 +16427,7 @@
       <c r="I41" s="86"/>
       <c r="J41" s="86"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B42" s="86"/>
       <c r="C42" s="86"/>
       <c r="D42" s="86"/>
@@ -16441,7 +16438,7 @@
       <c r="I42" s="86"/>
       <c r="J42" s="86"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B43" s="86"/>
       <c r="C43" s="86"/>
       <c r="D43" s="86"/>
@@ -16452,7 +16449,7 @@
       <c r="I43" s="86"/>
       <c r="J43" s="86"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B44" s="86"/>
       <c r="C44" s="86"/>
       <c r="D44" s="86"/>
@@ -16463,7 +16460,7 @@
       <c r="I44" s="86"/>
       <c r="J44" s="86"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B45" s="86"/>
       <c r="C45" s="86"/>
       <c r="D45" s="86"/>
@@ -16474,7 +16471,7 @@
       <c r="I45" s="86"/>
       <c r="J45" s="86"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B46" s="86"/>
       <c r="C46" s="86"/>
       <c r="D46" s="86"/>
@@ -16485,7 +16482,7 @@
       <c r="I46" s="86"/>
       <c r="J46" s="86"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B47" s="86"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -16496,7 +16493,7 @@
       <c r="I47" s="86"/>
       <c r="J47" s="86"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B48" s="86"/>
       <c r="C48" s="86"/>
       <c r="D48" s="86"/>
@@ -16507,7 +16504,7 @@
       <c r="I48" s="86"/>
       <c r="J48" s="86"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B49" s="86"/>
       <c r="C49" s="86"/>
       <c r="D49" s="86"/>
@@ -16518,7 +16515,7 @@
       <c r="I49" s="86"/>
       <c r="J49" s="86"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B50" s="86"/>
       <c r="C50" s="86"/>
       <c r="D50" s="86"/>
@@ -16529,7 +16526,7 @@
       <c r="I50" s="86"/>
       <c r="J50" s="86"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B51" s="86"/>
       <c r="C51" s="86"/>
       <c r="D51" s="86"/>
@@ -16540,7 +16537,7 @@
       <c r="I51" s="86"/>
       <c r="J51" s="86"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B52" s="86"/>
       <c r="C52" s="86"/>
       <c r="D52" s="86"/>
@@ -16551,7 +16548,7 @@
       <c r="I52" s="86"/>
       <c r="J52" s="86"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B53" s="86"/>
       <c r="C53" s="86"/>
       <c r="D53" s="86"/>
@@ -16562,7 +16559,7 @@
       <c r="I53" s="86"/>
       <c r="J53" s="86"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B54" s="86"/>
       <c r="C54" s="86"/>
       <c r="D54" s="86"/>
@@ -16573,7 +16570,7 @@
       <c r="I54" s="86"/>
       <c r="J54" s="86"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B55" s="86"/>
       <c r="C55" s="86"/>
       <c r="D55" s="86"/>
@@ -16584,7 +16581,7 @@
       <c r="I55" s="86"/>
       <c r="J55" s="86"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B56" s="86"/>
       <c r="C56" s="86"/>
       <c r="D56" s="86"/>
@@ -16595,7 +16592,7 @@
       <c r="I56" s="86"/>
       <c r="J56" s="86"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B57" s="86"/>
       <c r="C57" s="86"/>
       <c r="D57" s="86"/>
@@ -16606,7 +16603,7 @@
       <c r="I57" s="86"/>
       <c r="J57" s="86"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B58" s="86"/>
       <c r="C58" s="86"/>
       <c r="D58" s="86"/>
@@ -16617,7 +16614,7 @@
       <c r="I58" s="86"/>
       <c r="J58" s="86"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B59" s="86"/>
       <c r="C59" s="86"/>
       <c r="D59" s="86"/>
@@ -16628,7 +16625,7 @@
       <c r="I59" s="86"/>
       <c r="J59" s="86"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B60" s="86"/>
       <c r="C60" s="86"/>
       <c r="D60" s="86"/>
@@ -16639,7 +16636,7 @@
       <c r="I60" s="86"/>
       <c r="J60" s="86"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B61" s="86"/>
       <c r="C61" s="86"/>
       <c r="D61" s="86"/>
@@ -16650,7 +16647,7 @@
       <c r="I61" s="86"/>
       <c r="J61" s="86"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B62" s="86"/>
       <c r="C62" s="86"/>
       <c r="D62" s="86"/>
@@ -16661,7 +16658,7 @@
       <c r="I62" s="86"/>
       <c r="J62" s="86"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B63" s="86"/>
       <c r="C63" s="86"/>
       <c r="D63" s="86"/>
@@ -16672,7 +16669,7 @@
       <c r="I63" s="86"/>
       <c r="J63" s="86"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B64" s="86"/>
       <c r="C64" s="86"/>
       <c r="D64" s="86"/>
@@ -16683,7 +16680,7 @@
       <c r="I64" s="86"/>
       <c r="J64" s="86"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B65" s="86"/>
       <c r="C65" s="86"/>
       <c r="D65" s="86"/>
@@ -16694,7 +16691,7 @@
       <c r="I65" s="86"/>
       <c r="J65" s="86"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B66" s="86"/>
       <c r="C66" s="86"/>
       <c r="D66" s="86"/>
@@ -16705,7 +16702,7 @@
       <c r="I66" s="86"/>
       <c r="J66" s="86"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B67" s="86"/>
       <c r="C67" s="86"/>
       <c r="D67" s="86"/>
@@ -16716,7 +16713,7 @@
       <c r="I67" s="86"/>
       <c r="J67" s="86"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B68" s="86"/>
       <c r="C68" s="86"/>
       <c r="D68" s="86"/>
@@ -16727,7 +16724,7 @@
       <c r="I68" s="86"/>
       <c r="J68" s="86"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B69" s="86"/>
       <c r="C69" s="86"/>
       <c r="D69" s="86"/>
@@ -16738,7 +16735,7 @@
       <c r="I69" s="86"/>
       <c r="J69" s="86"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B70" s="86"/>
       <c r="C70" s="86"/>
       <c r="D70" s="86"/>
@@ -16749,7 +16746,7 @@
       <c r="I70" s="86"/>
       <c r="J70" s="86"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B71" s="86"/>
       <c r="C71" s="86"/>
       <c r="D71" s="86"/>
@@ -16760,7 +16757,7 @@
       <c r="I71" s="86"/>
       <c r="J71" s="86"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B72" s="86"/>
       <c r="C72" s="86"/>
       <c r="D72" s="86"/>
@@ -16771,7 +16768,7 @@
       <c r="I72" s="86"/>
       <c r="J72" s="86"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B73" s="86"/>
       <c r="C73" s="86"/>
       <c r="D73" s="86"/>
@@ -16782,7 +16779,7 @@
       <c r="I73" s="86"/>
       <c r="J73" s="86"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B74" s="86"/>
       <c r="C74" s="86"/>
       <c r="D74" s="86"/>
@@ -16793,7 +16790,7 @@
       <c r="I74" s="86"/>
       <c r="J74" s="86"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B75" s="86"/>
       <c r="C75" s="86"/>
       <c r="D75" s="86"/>
@@ -16804,7 +16801,7 @@
       <c r="I75" s="86"/>
       <c r="J75" s="86"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B76" s="86"/>
       <c r="C76" s="86"/>
       <c r="D76" s="86"/>
@@ -16815,7 +16812,7 @@
       <c r="I76" s="86"/>
       <c r="J76" s="86"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B77" s="86"/>
       <c r="C77" s="86"/>
       <c r="D77" s="86"/>
@@ -16826,7 +16823,7 @@
       <c r="I77" s="86"/>
       <c r="J77" s="86"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B78" s="86"/>
       <c r="C78" s="86"/>
       <c r="D78" s="86"/>
@@ -16837,7 +16834,7 @@
       <c r="I78" s="86"/>
       <c r="J78" s="86"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B79" s="86"/>
       <c r="C79" s="86"/>
       <c r="D79" s="86"/>
@@ -16848,7 +16845,7 @@
       <c r="I79" s="86"/>
       <c r="J79" s="86"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B80" s="86"/>
       <c r="C80" s="86"/>
       <c r="D80" s="86"/>
@@ -16859,7 +16856,7 @@
       <c r="I80" s="86"/>
       <c r="J80" s="86"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B81" s="86"/>
       <c r="C81" s="86"/>
       <c r="D81" s="86"/>
@@ -16870,7 +16867,7 @@
       <c r="I81" s="86"/>
       <c r="J81" s="86"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B82" s="86"/>
       <c r="C82" s="86"/>
       <c r="D82" s="86"/>
@@ -16881,7 +16878,7 @@
       <c r="I82" s="86"/>
       <c r="J82" s="86"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B83" s="86"/>
       <c r="C83" s="86"/>
       <c r="D83" s="86"/>
@@ -16892,7 +16889,7 @@
       <c r="I83" s="86"/>
       <c r="J83" s="86"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B84" s="86"/>
       <c r="C84" s="86"/>
       <c r="D84" s="86"/>
@@ -16903,7 +16900,7 @@
       <c r="I84" s="86"/>
       <c r="J84" s="86"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B85" s="86"/>
       <c r="C85" s="86"/>
       <c r="D85" s="86"/>
@@ -16914,7 +16911,7 @@
       <c r="I85" s="86"/>
       <c r="J85" s="86"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B86" s="86"/>
       <c r="C86" s="86"/>
       <c r="D86" s="86"/>
@@ -16925,7 +16922,7 @@
       <c r="I86" s="86"/>
       <c r="J86" s="86"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B87" s="86"/>
       <c r="C87" s="86"/>
       <c r="D87" s="86"/>
@@ -16936,7 +16933,7 @@
       <c r="I87" s="86"/>
       <c r="J87" s="86"/>
     </row>
-    <row r="88" spans="2:10">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B88" s="86"/>
       <c r="C88" s="86"/>
       <c r="D88" s="86"/>
@@ -16947,7 +16944,7 @@
       <c r="I88" s="86"/>
       <c r="J88" s="86"/>
     </row>
-    <row r="89" spans="2:10">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B89" s="86"/>
       <c r="C89" s="86"/>
       <c r="D89" s="86"/>
@@ -16958,7 +16955,7 @@
       <c r="I89" s="86"/>
       <c r="J89" s="86"/>
     </row>
-    <row r="90" spans="2:10">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B90" s="86"/>
       <c r="C90" s="86"/>
       <c r="D90" s="86"/>
@@ -16969,7 +16966,7 @@
       <c r="I90" s="86"/>
       <c r="J90" s="86"/>
     </row>
-    <row r="91" spans="2:10">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B91" s="86"/>
       <c r="C91" s="86"/>
       <c r="D91" s="86"/>
@@ -16980,7 +16977,7 @@
       <c r="I91" s="86"/>
       <c r="J91" s="86"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B92" s="86"/>
       <c r="C92" s="86"/>
       <c r="D92" s="86"/>
@@ -16991,7 +16988,7 @@
       <c r="I92" s="86"/>
       <c r="J92" s="86"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B93" s="86"/>
       <c r="C93" s="86"/>
       <c r="D93" s="86"/>
@@ -17002,7 +16999,7 @@
       <c r="I93" s="86"/>
       <c r="J93" s="86"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B94" s="86"/>
       <c r="C94" s="86"/>
       <c r="D94" s="86"/>
@@ -17013,7 +17010,7 @@
       <c r="I94" s="86"/>
       <c r="J94" s="86"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B95" s="86"/>
       <c r="C95" s="86"/>
       <c r="D95" s="86"/>
@@ -17024,7 +17021,7 @@
       <c r="I95" s="86"/>
       <c r="J95" s="86"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B96" s="86"/>
       <c r="C96" s="86"/>
       <c r="D96" s="86"/>
@@ -17035,7 +17032,7 @@
       <c r="I96" s="86"/>
       <c r="J96" s="86"/>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B97" s="86"/>
       <c r="C97" s="86"/>
       <c r="D97" s="86"/>
@@ -17046,7 +17043,7 @@
       <c r="I97" s="86"/>
       <c r="J97" s="86"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B98" s="86"/>
       <c r="C98" s="86"/>
       <c r="D98" s="86"/>
@@ -17057,7 +17054,7 @@
       <c r="I98" s="86"/>
       <c r="J98" s="86"/>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B99" s="86"/>
       <c r="C99" s="86"/>
       <c r="D99" s="86"/>
@@ -17068,7 +17065,7 @@
       <c r="I99" s="86"/>
       <c r="J99" s="86"/>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B100" s="86"/>
       <c r="C100" s="86"/>
       <c r="D100" s="86"/>
@@ -17079,7 +17076,7 @@
       <c r="I100" s="86"/>
       <c r="J100" s="86"/>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B101" s="86"/>
       <c r="C101" s="86"/>
       <c r="D101" s="86"/>
@@ -17090,7 +17087,7 @@
       <c r="I101" s="86"/>
       <c r="J101" s="86"/>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B102" s="86"/>
       <c r="C102" s="86"/>
       <c r="D102" s="86"/>
@@ -17101,7 +17098,7 @@
       <c r="I102" s="86"/>
       <c r="J102" s="86"/>
     </row>
-    <row r="103" spans="2:10">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B103" s="86"/>
       <c r="C103" s="86"/>
       <c r="D103" s="86"/>
@@ -17112,7 +17109,7 @@
       <c r="I103" s="86"/>
       <c r="J103" s="86"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B104" s="86"/>
       <c r="C104" s="86"/>
       <c r="D104" s="86"/>
@@ -17123,7 +17120,7 @@
       <c r="I104" s="86"/>
       <c r="J104" s="86"/>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B105" s="86"/>
       <c r="C105" s="86"/>
       <c r="D105" s="86"/>
@@ -17134,7 +17131,7 @@
       <c r="I105" s="86"/>
       <c r="J105" s="86"/>
     </row>
-    <row r="106" spans="2:10">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B106" s="86"/>
       <c r="C106" s="86"/>
       <c r="D106" s="86"/>
@@ -17145,7 +17142,7 @@
       <c r="I106" s="86"/>
       <c r="J106" s="86"/>
     </row>
-    <row r="107" spans="2:10">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B107" s="86"/>
       <c r="C107" s="86"/>
       <c r="D107" s="86"/>
@@ -17156,7 +17153,7 @@
       <c r="I107" s="86"/>
       <c r="J107" s="86"/>
     </row>
-    <row r="108" spans="2:10">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B108" s="86"/>
       <c r="C108" s="86"/>
       <c r="D108" s="86"/>
@@ -17167,7 +17164,7 @@
       <c r="I108" s="86"/>
       <c r="J108" s="86"/>
     </row>
-    <row r="109" spans="2:10">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B109" s="86"/>
       <c r="C109" s="86"/>
       <c r="D109" s="86"/>
@@ -17178,7 +17175,7 @@
       <c r="I109" s="86"/>
       <c r="J109" s="86"/>
     </row>
-    <row r="110" spans="2:10">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B110" s="86"/>
       <c r="C110" s="86"/>
       <c r="D110" s="86"/>
@@ -17189,7 +17186,7 @@
       <c r="I110" s="86"/>
       <c r="J110" s="86"/>
     </row>
-    <row r="111" spans="2:10">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B111" s="86"/>
       <c r="C111" s="86"/>
       <c r="D111" s="86"/>
@@ -17200,7 +17197,7 @@
       <c r="I111" s="86"/>
       <c r="J111" s="86"/>
     </row>
-    <row r="112" spans="2:10">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B112" s="86"/>
       <c r="C112" s="86"/>
       <c r="D112" s="86"/>
@@ -17211,7 +17208,7 @@
       <c r="I112" s="86"/>
       <c r="J112" s="86"/>
     </row>
-    <row r="113" spans="2:10">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B113" s="86"/>
       <c r="C113" s="86"/>
       <c r="D113" s="86"/>
@@ -17222,7 +17219,7 @@
       <c r="I113" s="86"/>
       <c r="J113" s="86"/>
     </row>
-    <row r="114" spans="2:10">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B114" s="86"/>
       <c r="C114" s="86"/>
       <c r="D114" s="86"/>
@@ -17233,7 +17230,7 @@
       <c r="I114" s="86"/>
       <c r="J114" s="86"/>
     </row>
-    <row r="115" spans="2:10">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B115" s="86"/>
       <c r="C115" s="86"/>
       <c r="D115" s="86"/>
@@ -17244,7 +17241,7 @@
       <c r="I115" s="86"/>
       <c r="J115" s="86"/>
     </row>
-    <row r="116" spans="2:10">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B116" s="86"/>
       <c r="C116" s="86"/>
       <c r="D116" s="86"/>
@@ -17255,7 +17252,7 @@
       <c r="I116" s="86"/>
       <c r="J116" s="86"/>
     </row>
-    <row r="117" spans="2:10">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B117" s="86"/>
       <c r="C117" s="86"/>
       <c r="D117" s="86"/>
@@ -17266,7 +17263,7 @@
       <c r="I117" s="86"/>
       <c r="J117" s="86"/>
     </row>
-    <row r="118" spans="2:10">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B118" s="86"/>
       <c r="C118" s="86"/>
       <c r="D118" s="86"/>
@@ -17277,7 +17274,7 @@
       <c r="I118" s="86"/>
       <c r="J118" s="86"/>
     </row>
-    <row r="119" spans="2:10">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B119" s="86"/>
       <c r="C119" s="86"/>
       <c r="D119" s="86"/>
@@ -17288,7 +17285,7 @@
       <c r="I119" s="86"/>
       <c r="J119" s="86"/>
     </row>
-    <row r="120" spans="2:10">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B120" s="86"/>
       <c r="C120" s="86"/>
       <c r="D120" s="86"/>
@@ -17299,7 +17296,7 @@
       <c r="I120" s="86"/>
       <c r="J120" s="86"/>
     </row>
-    <row r="121" spans="2:10">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B121" s="86"/>
       <c r="C121" s="86"/>
       <c r="D121" s="86"/>
@@ -17310,7 +17307,7 @@
       <c r="I121" s="86"/>
       <c r="J121" s="86"/>
     </row>
-    <row r="122" spans="2:10">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B122" s="86"/>
       <c r="C122" s="86"/>
       <c r="D122" s="86"/>
@@ -17321,7 +17318,7 @@
       <c r="I122" s="86"/>
       <c r="J122" s="86"/>
     </row>
-    <row r="123" spans="2:10">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B123" s="86"/>
       <c r="C123" s="86"/>
       <c r="D123" s="86"/>
@@ -17332,7 +17329,7 @@
       <c r="I123" s="86"/>
       <c r="J123" s="86"/>
     </row>
-    <row r="124" spans="2:10">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B124" s="86"/>
       <c r="C124" s="86"/>
       <c r="D124" s="86"/>
@@ -17343,7 +17340,7 @@
       <c r="I124" s="86"/>
       <c r="J124" s="86"/>
     </row>
-    <row r="125" spans="2:10">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B125" s="86"/>
       <c r="C125" s="86"/>
       <c r="D125" s="86"/>
@@ -17354,7 +17351,7 @@
       <c r="I125" s="86"/>
       <c r="J125" s="86"/>
     </row>
-    <row r="126" spans="2:10">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B126" s="86"/>
       <c r="C126" s="86"/>
       <c r="D126" s="86"/>
@@ -17365,7 +17362,7 @@
       <c r="I126" s="86"/>
       <c r="J126" s="86"/>
     </row>
-    <row r="127" spans="2:10">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B127" s="86"/>
       <c r="C127" s="86"/>
       <c r="D127" s="86"/>
@@ -17376,7 +17373,7 @@
       <c r="I127" s="86"/>
       <c r="J127" s="86"/>
     </row>
-    <row r="128" spans="2:10">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B128" s="86"/>
       <c r="C128" s="86"/>
       <c r="D128" s="86"/>
@@ -17387,7 +17384,7 @@
       <c r="I128" s="86"/>
       <c r="J128" s="86"/>
     </row>
-    <row r="129" spans="2:10">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B129" s="86"/>
       <c r="C129" s="86"/>
       <c r="D129" s="86"/>
@@ -17398,7 +17395,7 @@
       <c r="I129" s="86"/>
       <c r="J129" s="86"/>
     </row>
-    <row r="130" spans="2:10">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B130" s="86"/>
       <c r="C130" s="86"/>
       <c r="D130" s="86"/>
@@ -17409,7 +17406,7 @@
       <c r="I130" s="86"/>
       <c r="J130" s="86"/>
     </row>
-    <row r="131" spans="2:10">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B131" s="86"/>
       <c r="C131" s="86"/>
       <c r="D131" s="86"/>
@@ -17420,7 +17417,7 @@
       <c r="I131" s="86"/>
       <c r="J131" s="86"/>
     </row>
-    <row r="132" spans="2:10">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B132" s="86"/>
       <c r="C132" s="86"/>
       <c r="D132" s="86"/>
@@ -17431,7 +17428,7 @@
       <c r="I132" s="86"/>
       <c r="J132" s="86"/>
     </row>
-    <row r="133" spans="2:10">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B133" s="86"/>
       <c r="C133" s="86"/>
       <c r="D133" s="86"/>
@@ -17442,7 +17439,7 @@
       <c r="I133" s="86"/>
       <c r="J133" s="86"/>
     </row>
-    <row r="134" spans="2:10">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B134" s="86"/>
       <c r="C134" s="86"/>
       <c r="D134" s="86"/>
@@ -17453,7 +17450,7 @@
       <c r="I134" s="86"/>
       <c r="J134" s="86"/>
     </row>
-    <row r="135" spans="2:10">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B135" s="86"/>
       <c r="C135" s="86"/>
       <c r="D135" s="86"/>
@@ -17464,7 +17461,7 @@
       <c r="I135" s="86"/>
       <c r="J135" s="86"/>
     </row>
-    <row r="136" spans="2:10">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B136" s="86"/>
       <c r="C136" s="86"/>
       <c r="D136" s="86"/>
@@ -17475,7 +17472,7 @@
       <c r="I136" s="86"/>
       <c r="J136" s="86"/>
     </row>
-    <row r="137" spans="2:10">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B137" s="86"/>
       <c r="C137" s="86"/>
       <c r="D137" s="86"/>
@@ -17486,7 +17483,7 @@
       <c r="I137" s="86"/>
       <c r="J137" s="86"/>
     </row>
-    <row r="138" spans="2:10">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B138" s="86"/>
       <c r="C138" s="86"/>
       <c r="D138" s="86"/>
@@ -17497,7 +17494,7 @@
       <c r="I138" s="86"/>
       <c r="J138" s="86"/>
     </row>
-    <row r="139" spans="2:10">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B139" s="86"/>
       <c r="C139" s="86"/>
       <c r="D139" s="86"/>
@@ -17508,7 +17505,7 @@
       <c r="I139" s="86"/>
       <c r="J139" s="86"/>
     </row>
-    <row r="140" spans="2:10">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B140" s="86"/>
       <c r="C140" s="86"/>
       <c r="D140" s="86"/>
@@ -17519,7 +17516,7 @@
       <c r="I140" s="86"/>
       <c r="J140" s="86"/>
     </row>
-    <row r="141" spans="2:10">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B141" s="86"/>
       <c r="C141" s="86"/>
       <c r="D141" s="86"/>
@@ -17530,7 +17527,7 @@
       <c r="I141" s="86"/>
       <c r="J141" s="86"/>
     </row>
-    <row r="142" spans="2:10">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B142" s="86"/>
       <c r="C142" s="86"/>
       <c r="D142" s="86"/>
@@ -17541,7 +17538,7 @@
       <c r="I142" s="86"/>
       <c r="J142" s="86"/>
     </row>
-    <row r="143" spans="2:10">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B143" s="86"/>
       <c r="C143" s="86"/>
       <c r="D143" s="86"/>
@@ -17552,7 +17549,7 @@
       <c r="I143" s="86"/>
       <c r="J143" s="86"/>
     </row>
-    <row r="144" spans="2:10">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B144" s="86"/>
       <c r="C144" s="86"/>
       <c r="D144" s="86"/>
@@ -17563,7 +17560,7 @@
       <c r="I144" s="86"/>
       <c r="J144" s="86"/>
     </row>
-    <row r="145" spans="2:10">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B145" s="86"/>
       <c r="C145" s="86"/>
       <c r="D145" s="86"/>
@@ -17574,7 +17571,7 @@
       <c r="I145" s="86"/>
       <c r="J145" s="86"/>
     </row>
-    <row r="146" spans="2:10">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B146" s="86"/>
       <c r="C146" s="86"/>
       <c r="D146" s="86"/>
@@ -17585,7 +17582,7 @@
       <c r="I146" s="86"/>
       <c r="J146" s="86"/>
     </row>
-    <row r="147" spans="2:10">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B147" s="86"/>
       <c r="C147" s="86"/>
       <c r="D147" s="86"/>
@@ -17596,7 +17593,7 @@
       <c r="I147" s="86"/>
       <c r="J147" s="86"/>
     </row>
-    <row r="148" spans="2:10">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B148" s="86"/>
       <c r="C148" s="86"/>
       <c r="D148" s="86"/>
@@ -17607,7 +17604,7 @@
       <c r="I148" s="86"/>
       <c r="J148" s="86"/>
     </row>
-    <row r="149" spans="2:10">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B149" s="86"/>
       <c r="C149" s="86"/>
       <c r="D149" s="86"/>
@@ -17618,7 +17615,7 @@
       <c r="I149" s="86"/>
       <c r="J149" s="86"/>
     </row>
-    <row r="150" spans="2:10">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B150" s="86"/>
       <c r="C150" s="86"/>
       <c r="D150" s="86"/>
@@ -17629,7 +17626,7 @@
       <c r="I150" s="86"/>
       <c r="J150" s="86"/>
     </row>
-    <row r="151" spans="2:10">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B151" s="86"/>
       <c r="C151" s="86"/>
       <c r="D151" s="86"/>
@@ -17640,7 +17637,7 @@
       <c r="I151" s="86"/>
       <c r="J151" s="86"/>
     </row>
-    <row r="152" spans="2:10">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B152" s="86"/>
       <c r="C152" s="86"/>
       <c r="D152" s="86"/>
@@ -17651,7 +17648,7 @@
       <c r="I152" s="86"/>
       <c r="J152" s="86"/>
     </row>
-    <row r="153" spans="2:10">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B153" s="86"/>
       <c r="C153" s="86"/>
       <c r="D153" s="86"/>
@@ -17662,7 +17659,7 @@
       <c r="I153" s="86"/>
       <c r="J153" s="86"/>
     </row>
-    <row r="154" spans="2:10">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B154" s="86"/>
       <c r="C154" s="86"/>
       <c r="D154" s="86"/>
@@ -17673,7 +17670,7 @@
       <c r="I154" s="86"/>
       <c r="J154" s="86"/>
     </row>
-    <row r="155" spans="2:10">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B155" s="86"/>
       <c r="C155" s="86"/>
       <c r="D155" s="86"/>
@@ -17684,7 +17681,7 @@
       <c r="I155" s="86"/>
       <c r="J155" s="86"/>
     </row>
-    <row r="156" spans="2:10">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B156" s="86"/>
       <c r="C156" s="86"/>
       <c r="D156" s="86"/>
@@ -17695,7 +17692,7 @@
       <c r="I156" s="86"/>
       <c r="J156" s="86"/>
     </row>
-    <row r="157" spans="2:10">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B157" s="86"/>
       <c r="C157" s="86"/>
       <c r="D157" s="86"/>
@@ -17706,7 +17703,7 @@
       <c r="I157" s="86"/>
       <c r="J157" s="86"/>
     </row>
-    <row r="158" spans="2:10">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B158" s="86"/>
       <c r="C158" s="86"/>
       <c r="D158" s="86"/>
@@ -17717,7 +17714,7 @@
       <c r="I158" s="86"/>
       <c r="J158" s="86"/>
     </row>
-    <row r="159" spans="2:10">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B159" s="86"/>
       <c r="C159" s="86"/>
       <c r="D159" s="86"/>
@@ -17728,7 +17725,7 @@
       <c r="I159" s="86"/>
       <c r="J159" s="86"/>
     </row>
-    <row r="160" spans="2:10">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B160" s="86"/>
       <c r="C160" s="86"/>
       <c r="D160" s="86"/>
@@ -17739,7 +17736,7 @@
       <c r="I160" s="86"/>
       <c r="J160" s="86"/>
     </row>
-    <row r="161" spans="2:10">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B161" s="86"/>
       <c r="C161" s="86"/>
       <c r="D161" s="86"/>
@@ -17750,7 +17747,7 @@
       <c r="I161" s="86"/>
       <c r="J161" s="86"/>
     </row>
-    <row r="162" spans="2:10">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B162" s="86"/>
       <c r="C162" s="86"/>
       <c r="D162" s="86"/>
@@ -17761,7 +17758,7 @@
       <c r="I162" s="86"/>
       <c r="J162" s="86"/>
     </row>
-    <row r="163" spans="2:10">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B163" s="86"/>
       <c r="C163" s="86"/>
       <c r="D163" s="86"/>
@@ -17772,7 +17769,7 @@
       <c r="I163" s="86"/>
       <c r="J163" s="86"/>
     </row>
-    <row r="164" spans="2:10">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B164" s="86"/>
       <c r="C164" s="86"/>
       <c r="D164" s="86"/>
@@ -17783,7 +17780,7 @@
       <c r="I164" s="86"/>
       <c r="J164" s="86"/>
     </row>
-    <row r="165" spans="2:10">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B165" s="86"/>
       <c r="C165" s="86"/>
       <c r="D165" s="86"/>
@@ -17794,7 +17791,7 @@
       <c r="I165" s="86"/>
       <c r="J165" s="86"/>
     </row>
-    <row r="166" spans="2:10">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B166" s="86"/>
       <c r="C166" s="86"/>
       <c r="D166" s="86"/>
@@ -17805,7 +17802,7 @@
       <c r="I166" s="86"/>
       <c r="J166" s="86"/>
     </row>
-    <row r="167" spans="2:10">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B167" s="86"/>
       <c r="C167" s="86"/>
       <c r="D167" s="86"/>
@@ -17816,7 +17813,7 @@
       <c r="I167" s="86"/>
       <c r="J167" s="86"/>
     </row>
-    <row r="168" spans="2:10">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B168" s="86"/>
       <c r="C168" s="86"/>
       <c r="D168" s="86"/>
@@ -17827,7 +17824,7 @@
       <c r="I168" s="86"/>
       <c r="J168" s="86"/>
     </row>
-    <row r="169" spans="2:10">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B169" s="86"/>
       <c r="C169" s="86"/>
       <c r="D169" s="86"/>
@@ -17838,7 +17835,7 @@
       <c r="I169" s="86"/>
       <c r="J169" s="86"/>
     </row>
-    <row r="170" spans="2:10">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B170" s="86"/>
       <c r="C170" s="86"/>
       <c r="D170" s="86"/>
@@ -17849,7 +17846,7 @@
       <c r="I170" s="86"/>
       <c r="J170" s="86"/>
     </row>
-    <row r="171" spans="2:10">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B171" s="86"/>
       <c r="C171" s="86"/>
       <c r="D171" s="86"/>
@@ -17860,7 +17857,7 @@
       <c r="I171" s="86"/>
       <c r="J171" s="86"/>
     </row>
-    <row r="172" spans="2:10">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B172" s="86"/>
       <c r="C172" s="86"/>
       <c r="D172" s="86"/>
@@ -17871,7 +17868,7 @@
       <c r="I172" s="86"/>
       <c r="J172" s="86"/>
     </row>
-    <row r="173" spans="2:10">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B173" s="86"/>
       <c r="C173" s="86"/>
       <c r="D173" s="86"/>
@@ -17882,7 +17879,7 @@
       <c r="I173" s="86"/>
       <c r="J173" s="86"/>
     </row>
-    <row r="174" spans="2:10">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B174" s="86"/>
       <c r="C174" s="86"/>
       <c r="D174" s="86"/>
@@ -17893,7 +17890,7 @@
       <c r="I174" s="86"/>
       <c r="J174" s="86"/>
     </row>
-    <row r="175" spans="2:10">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B175" s="86"/>
       <c r="C175" s="86"/>
       <c r="D175" s="86"/>
@@ -17904,7 +17901,7 @@
       <c r="I175" s="86"/>
       <c r="J175" s="86"/>
     </row>
-    <row r="176" spans="2:10">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B176" s="86"/>
       <c r="C176" s="86"/>
       <c r="D176" s="86"/>
@@ -17915,7 +17912,7 @@
       <c r="I176" s="86"/>
       <c r="J176" s="86"/>
     </row>
-    <row r="177" spans="2:10">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B177" s="86"/>
       <c r="C177" s="86"/>
       <c r="D177" s="86"/>
@@ -17926,7 +17923,7 @@
       <c r="I177" s="86"/>
       <c r="J177" s="86"/>
     </row>
-    <row r="178" spans="2:10">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B178" s="86"/>
       <c r="C178" s="86"/>
       <c r="D178" s="86"/>
@@ -17937,7 +17934,7 @@
       <c r="I178" s="86"/>
       <c r="J178" s="86"/>
     </row>
-    <row r="179" spans="2:10">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B179" s="86"/>
       <c r="C179" s="86"/>
       <c r="D179" s="86"/>
@@ -17948,7 +17945,7 @@
       <c r="I179" s="86"/>
       <c r="J179" s="86"/>
     </row>
-    <row r="180" spans="2:10">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B180" s="86"/>
       <c r="C180" s="86"/>
       <c r="D180" s="86"/>
@@ -17959,7 +17956,7 @@
       <c r="I180" s="86"/>
       <c r="J180" s="86"/>
     </row>
-    <row r="181" spans="2:10">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B181" s="86"/>
       <c r="C181" s="86"/>
       <c r="D181" s="86"/>
@@ -17970,7 +17967,7 @@
       <c r="I181" s="86"/>
       <c r="J181" s="86"/>
     </row>
-    <row r="182" spans="2:10">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B182" s="86"/>
       <c r="C182" s="86"/>
       <c r="D182" s="86"/>
@@ -17981,7 +17978,7 @@
       <c r="I182" s="86"/>
       <c r="J182" s="86"/>
     </row>
-    <row r="183" spans="2:10">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B183" s="86"/>
       <c r="C183" s="86"/>
       <c r="D183" s="86"/>
@@ -17992,7 +17989,7 @@
       <c r="I183" s="86"/>
       <c r="J183" s="86"/>
     </row>
-    <row r="184" spans="2:10">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B184" s="86"/>
       <c r="C184" s="86"/>
       <c r="D184" s="86"/>
@@ -18003,7 +18000,7 @@
       <c r="I184" s="86"/>
       <c r="J184" s="86"/>
     </row>
-    <row r="185" spans="2:10">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B185" s="86"/>
       <c r="C185" s="86"/>
       <c r="D185" s="86"/>
@@ -18014,7 +18011,7 @@
       <c r="I185" s="86"/>
       <c r="J185" s="86"/>
     </row>
-    <row r="186" spans="2:10">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B186" s="86"/>
       <c r="C186" s="86"/>
       <c r="D186" s="86"/>
@@ -18025,7 +18022,7 @@
       <c r="I186" s="86"/>
       <c r="J186" s="86"/>
     </row>
-    <row r="187" spans="2:10">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B187" s="86"/>
       <c r="C187" s="86"/>
       <c r="D187" s="86"/>
@@ -18036,7 +18033,7 @@
       <c r="I187" s="86"/>
       <c r="J187" s="86"/>
     </row>
-    <row r="188" spans="2:10">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B188" s="86"/>
       <c r="C188" s="86"/>
       <c r="D188" s="86"/>
@@ -18047,7 +18044,7 @@
       <c r="I188" s="86"/>
       <c r="J188" s="86"/>
     </row>
-    <row r="189" spans="2:10">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B189" s="86"/>
       <c r="C189" s="86"/>
       <c r="D189" s="86"/>
@@ -18058,7 +18055,7 @@
       <c r="I189" s="86"/>
       <c r="J189" s="86"/>
     </row>
-    <row r="190" spans="2:10">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B190" s="86"/>
       <c r="C190" s="86"/>
       <c r="D190" s="86"/>
@@ -18069,7 +18066,7 @@
       <c r="I190" s="86"/>
       <c r="J190" s="86"/>
     </row>
-    <row r="191" spans="2:10">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B191" s="86"/>
       <c r="C191" s="86"/>
       <c r="D191" s="86"/>
@@ -18080,7 +18077,7 @@
       <c r="I191" s="86"/>
       <c r="J191" s="86"/>
     </row>
-    <row r="192" spans="2:10">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B192" s="86"/>
       <c r="C192" s="86"/>
       <c r="D192" s="86"/>
@@ -18091,7 +18088,7 @@
       <c r="I192" s="86"/>
       <c r="J192" s="86"/>
     </row>
-    <row r="193" spans="2:10">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B193" s="86"/>
       <c r="C193" s="86"/>
       <c r="D193" s="86"/>
@@ -18102,7 +18099,7 @@
       <c r="I193" s="86"/>
       <c r="J193" s="86"/>
     </row>
-    <row r="194" spans="2:10">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B194" s="86"/>
       <c r="C194" s="86"/>
       <c r="D194" s="86"/>
@@ -18113,7 +18110,7 @@
       <c r="I194" s="86"/>
       <c r="J194" s="86"/>
     </row>
-    <row r="195" spans="2:10">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B195" s="86"/>
       <c r="C195" s="86"/>
       <c r="D195" s="86"/>
@@ -18124,7 +18121,7 @@
       <c r="I195" s="86"/>
       <c r="J195" s="86"/>
     </row>
-    <row r="196" spans="2:10">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B196" s="86"/>
       <c r="C196" s="86"/>
       <c r="D196" s="86"/>
@@ -18135,7 +18132,7 @@
       <c r="I196" s="86"/>
       <c r="J196" s="86"/>
     </row>
-    <row r="197" spans="2:10">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B197" s="86"/>
       <c r="C197" s="86"/>
       <c r="D197" s="86"/>
@@ -18146,7 +18143,7 @@
       <c r="I197" s="86"/>
       <c r="J197" s="86"/>
     </row>
-    <row r="198" spans="2:10">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B198" s="86"/>
       <c r="C198" s="86"/>
       <c r="D198" s="86"/>
@@ -18157,7 +18154,7 @@
       <c r="I198" s="86"/>
       <c r="J198" s="86"/>
     </row>
-    <row r="199" spans="2:10">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B199" s="86"/>
       <c r="C199" s="86"/>
       <c r="D199" s="86"/>
@@ -18168,7 +18165,7 @@
       <c r="I199" s="86"/>
       <c r="J199" s="86"/>
     </row>
-    <row r="200" spans="2:10">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B200" s="86"/>
       <c r="C200" s="86"/>
       <c r="D200" s="86"/>
@@ -18179,7 +18176,7 @@
       <c r="I200" s="86"/>
       <c r="J200" s="86"/>
     </row>
-    <row r="201" spans="2:10">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B201" s="86"/>
       <c r="C201" s="86"/>
       <c r="D201" s="86"/>
@@ -18190,7 +18187,7 @@
       <c r="I201" s="86"/>
       <c r="J201" s="86"/>
     </row>
-    <row r="202" spans="2:10">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B202" s="86"/>
       <c r="C202" s="86"/>
       <c r="D202" s="86"/>
@@ -18201,7 +18198,7 @@
       <c r="I202" s="86"/>
       <c r="J202" s="86"/>
     </row>
-    <row r="203" spans="2:10">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B203" s="86"/>
       <c r="C203" s="86"/>
       <c r="D203" s="86"/>
@@ -18212,7 +18209,7 @@
       <c r="I203" s="86"/>
       <c r="J203" s="86"/>
     </row>
-    <row r="204" spans="2:10">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B204" s="86"/>
       <c r="C204" s="86"/>
       <c r="D204" s="86"/>
@@ -18223,7 +18220,7 @@
       <c r="I204" s="86"/>
       <c r="J204" s="86"/>
     </row>
-    <row r="205" spans="2:10">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B205" s="86"/>
       <c r="C205" s="86"/>
       <c r="D205" s="86"/>
@@ -18234,7 +18231,7 @@
       <c r="I205" s="86"/>
       <c r="J205" s="86"/>
     </row>
-    <row r="206" spans="2:10">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B206" s="86"/>
       <c r="C206" s="86"/>
       <c r="D206" s="86"/>
@@ -18245,7 +18242,7 @@
       <c r="I206" s="86"/>
       <c r="J206" s="86"/>
     </row>
-    <row r="207" spans="2:10">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B207" s="86"/>
       <c r="C207" s="86"/>
       <c r="D207" s="86"/>
@@ -18256,7 +18253,7 @@
       <c r="I207" s="86"/>
       <c r="J207" s="86"/>
     </row>
-    <row r="208" spans="2:10">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B208" s="86"/>
       <c r="C208" s="86"/>
       <c r="D208" s="86"/>
@@ -18267,7 +18264,7 @@
       <c r="I208" s="86"/>
       <c r="J208" s="86"/>
     </row>
-    <row r="209" spans="2:10">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B209" s="86"/>
       <c r="C209" s="86"/>
       <c r="D209" s="86"/>
@@ -18278,7 +18275,7 @@
       <c r="I209" s="86"/>
       <c r="J209" s="86"/>
     </row>
-    <row r="210" spans="2:10">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B210" s="86"/>
       <c r="C210" s="86"/>
       <c r="D210" s="86"/>
@@ -18289,7 +18286,7 @@
       <c r="I210" s="86"/>
       <c r="J210" s="86"/>
     </row>
-    <row r="211" spans="2:10">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B211" s="86"/>
       <c r="C211" s="86"/>
       <c r="D211" s="86"/>
@@ -18300,7 +18297,7 @@
       <c r="I211" s="86"/>
       <c r="J211" s="86"/>
     </row>
-    <row r="212" spans="2:10">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B212" s="86"/>
       <c r="C212" s="86"/>
       <c r="D212" s="86"/>
@@ -18311,7 +18308,7 @@
       <c r="I212" s="86"/>
       <c r="J212" s="86"/>
     </row>
-    <row r="213" spans="2:10">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B213" s="86"/>
       <c r="C213" s="86"/>
       <c r="D213" s="86"/>
@@ -18322,7 +18319,7 @@
       <c r="I213" s="86"/>
       <c r="J213" s="86"/>
     </row>
-    <row r="214" spans="2:10">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B214" s="86"/>
       <c r="C214" s="86"/>
       <c r="D214" s="86"/>
@@ -18333,7 +18330,7 @@
       <c r="I214" s="86"/>
       <c r="J214" s="86"/>
     </row>
-    <row r="215" spans="2:10">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B215" s="86"/>
       <c r="C215" s="86"/>
       <c r="D215" s="86"/>
@@ -18344,7 +18341,7 @@
       <c r="I215" s="86"/>
       <c r="J215" s="86"/>
     </row>
-    <row r="216" spans="2:10">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B216" s="86"/>
       <c r="C216" s="86"/>
       <c r="D216" s="86"/>
@@ -18355,7 +18352,7 @@
       <c r="I216" s="86"/>
       <c r="J216" s="86"/>
     </row>
-    <row r="217" spans="2:10">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B217" s="86"/>
       <c r="C217" s="86"/>
       <c r="D217" s="86"/>
@@ -18366,7 +18363,7 @@
       <c r="I217" s="86"/>
       <c r="J217" s="86"/>
     </row>
-    <row r="218" spans="2:10">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B218" s="86"/>
       <c r="C218" s="86"/>
       <c r="D218" s="86"/>
@@ -18377,7 +18374,7 @@
       <c r="I218" s="86"/>
       <c r="J218" s="86"/>
     </row>
-    <row r="219" spans="2:10">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B219" s="86"/>
       <c r="C219" s="86"/>
       <c r="D219" s="86"/>
@@ -18388,7 +18385,7 @@
       <c r="I219" s="86"/>
       <c r="J219" s="86"/>
     </row>
-    <row r="220" spans="2:10">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B220" s="86"/>
       <c r="C220" s="86"/>
       <c r="D220" s="86"/>
@@ -18399,7 +18396,7 @@
       <c r="I220" s="86"/>
       <c r="J220" s="86"/>
     </row>
-    <row r="221" spans="2:10">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B221" s="86"/>
       <c r="C221" s="86"/>
       <c r="D221" s="86"/>
@@ -18410,7 +18407,7 @@
       <c r="I221" s="86"/>
       <c r="J221" s="86"/>
     </row>
-    <row r="222" spans="2:10">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B222" s="86"/>
       <c r="C222" s="86"/>
       <c r="D222" s="86"/>
@@ -18421,7 +18418,7 @@
       <c r="I222" s="86"/>
       <c r="J222" s="86"/>
     </row>
-    <row r="223" spans="2:10">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B223" s="86"/>
       <c r="C223" s="86"/>
       <c r="D223" s="86"/>
@@ -18432,7 +18429,7 @@
       <c r="I223" s="86"/>
       <c r="J223" s="86"/>
     </row>
-    <row r="224" spans="2:10">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B224" s="86"/>
       <c r="C224" s="86"/>
       <c r="D224" s="86"/>
@@ -18443,7 +18440,7 @@
       <c r="I224" s="86"/>
       <c r="J224" s="86"/>
     </row>
-    <row r="225" spans="2:10">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B225" s="86"/>
       <c r="C225" s="86"/>
       <c r="D225" s="86"/>
@@ -18454,7 +18451,7 @@
       <c r="I225" s="86"/>
       <c r="J225" s="86"/>
     </row>
-    <row r="226" spans="2:10">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B226" s="86"/>
       <c r="C226" s="86"/>
       <c r="D226" s="86"/>
@@ -18465,7 +18462,7 @@
       <c r="I226" s="86"/>
       <c r="J226" s="86"/>
     </row>
-    <row r="227" spans="2:10">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B227" s="86"/>
       <c r="C227" s="86"/>
       <c r="D227" s="86"/>
@@ -18476,7 +18473,7 @@
       <c r="I227" s="86"/>
       <c r="J227" s="86"/>
     </row>
-    <row r="228" spans="2:10">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B228" s="86"/>
       <c r="C228" s="86"/>
       <c r="D228" s="86"/>
@@ -18487,7 +18484,7 @@
       <c r="I228" s="86"/>
       <c r="J228" s="86"/>
     </row>
-    <row r="229" spans="2:10">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B229" s="86"/>
       <c r="C229" s="86"/>
       <c r="D229" s="86"/>
@@ -18498,7 +18495,7 @@
       <c r="I229" s="86"/>
       <c r="J229" s="86"/>
     </row>
-    <row r="230" spans="2:10">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B230" s="86"/>
       <c r="C230" s="86"/>
       <c r="D230" s="86"/>
@@ -18509,7 +18506,7 @@
       <c r="I230" s="86"/>
       <c r="J230" s="86"/>
     </row>
-    <row r="231" spans="2:10">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B231" s="86"/>
       <c r="C231" s="86"/>
       <c r="D231" s="86"/>
@@ -18520,7 +18517,7 @@
       <c r="I231" s="86"/>
       <c r="J231" s="86"/>
     </row>
-    <row r="409" spans="7:7">
+    <row r="409" spans="7:7" x14ac:dyDescent="0.4">
       <c r="G409" s="85"/>
     </row>
   </sheetData>
@@ -18534,18 +18531,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E800D6BD-E8A2-4105-8489-3C1271F91F5F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>60</v>
       </c>
@@ -18558,7 +18555,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -18571,7 +18568,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -18579,7 +18576,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -18587,7 +18584,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -18603,10 +18600,10 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -18666,18 +18663,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A7739A-7BBA-48AE-914B-6F018CF15AC7}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>68</v>
       </c>
@@ -18690,7 +18687,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -18703,12 +18700,12 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.4">
       <c r="L4" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -18724,14 +18721,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -18786,18 +18783,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F00CA0-C266-47C1-85A0-7C0D7A6C7D48}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:Y18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
@@ -18810,7 +18807,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -18823,7 +18820,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -18839,14 +18836,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -18890,7 +18887,7 @@
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C18" s="48"/>
     </row>
   </sheetData>
@@ -18904,18 +18901,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50657BE-863E-464A-9FD1-AAF9437A0AF4}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>34</v>
       </c>
@@ -18928,7 +18925,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -18941,7 +18938,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -18957,14 +18954,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -19019,18 +19016,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E65DD5-EC90-4E88-B620-AC1E30627D0B}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>38</v>
       </c>
@@ -19043,7 +19040,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -19056,7 +19053,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -19072,14 +19069,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -19134,18 +19131,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EF9FAA-5677-41DC-B67F-C3201AD61823}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>39</v>
       </c>
@@ -19158,7 +19155,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -19171,7 +19168,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -19187,14 +19184,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -19249,18 +19246,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D50FBA-2DD0-4E06-9323-B0FE551E6F0B}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>52</v>
       </c>
@@ -19273,7 +19270,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -19286,7 +19283,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -19302,14 +19299,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
@@ -19364,18 +19361,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DBE2A85-49D6-435E-B6C0-60FA67F2F058}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="32.69921875" customWidth="1"/>
+    <col min="5" max="6" width="18.69921875" customWidth="1"/>
+    <col min="7" max="7" width="23.69921875" customWidth="1"/>
+    <col min="8" max="10" width="8.69921875" customWidth="1"/>
+    <col min="11" max="11" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:25" ht="30" customHeight="1">
+    <row r="2" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>53</v>
       </c>
@@ -19388,7 +19385,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="82"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -19401,7 +19398,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B11" s="28">
         <f>COUNTA(B14:B1048576)</f>
         <v>0</v>
@@ -19417,14 +19414,14 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B13" s="77" t="s">
         <v>5</v>
       </c>
